--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486399_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486399_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3445</v>
+        <v>5.1924</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5686</v>
+        <v>2.7863</v>
       </c>
       <c r="F2" t="n">
-        <v>2.776</v>
+        <v>2.4061</v>
       </c>
       <c r="G2" t="n">
         <v>1.7582</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2145</v>
+        <v>1.0623</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1512</v>
+        <v>0.3689</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0632</v>
+        <v>0.6934</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0207</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1612</v>
+        <v>5.0359</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6472</v>
+        <v>2.4295</v>
       </c>
       <c r="F3" t="n">
-        <v>2.514</v>
+        <v>2.6065</v>
       </c>
       <c r="G3" t="n">
         <v>4.4426</v>
@@ -688,13 +688,13 @@
         <v>3.0451</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6714</v>
+        <v>0.2034</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0154</v>
+        <v>-0.2331</v>
       </c>
       <c r="U3" t="n">
-        <v>0.344</v>
+        <v>0.4365</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.341</v>
+        <v>2.8419</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4165</v>
+        <v>1.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9245</v>
+        <v>1.2019</v>
       </c>
       <c r="G4" t="n">
         <v>1.7312</v>
@@ -766,13 +766,13 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7175</v>
+        <v>-0.2166</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2019</v>
+        <v>0.0216</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5157</v>
+        <v>-0.2382</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5185999999999999</v>
+        <v>-0.1404</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3677</v>
+        <v>0.5853</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8491</v>
+        <v>-0.7258</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0233</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3668</v>
+        <v>0.7078</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0911</v>
+        <v>0.3088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2757</v>
+        <v>0.399</v>
       </c>
       <c r="V5" t="n">
         <v>-1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>C. LUTETE IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1345</v>
+        <v>-0.7731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7635</v>
+        <v>-1.5656</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.898</v>
+        <v>0.7926</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8454</v>
+        <v>1.6426</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9975000000000001</v>
+        <v>1.5239</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8478</v>
+        <v>0.1187</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5374</v>
+        <v>2.8109</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2492</v>
+        <v>2.5033</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7865</v>
+        <v>0.3076</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3827</v>
+        <v>-1.1683</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7484</v>
+        <v>-0.9794</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6344</v>
+        <v>-0.1889</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2965</v>
+        <v>0.6294</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7487</v>
+        <v>-0.0264</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5478</v>
+        <v>0.6558</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0207</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. LUTETE IV</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2105</v>
+        <v>-1.0828</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3421</v>
+        <v>-1.5256</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1316</v>
+        <v>0.4428</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6426</v>
+        <v>-0.84</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5239</v>
+        <v>-0.6448</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1187</v>
+        <v>-0.1952</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8109</v>
+        <v>-0.6886</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5033</v>
+        <v>-0.7268</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3076</v>
+        <v>0.0382</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1683</v>
+        <v>-0.1514</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9794</v>
+        <v>0.082</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1889</v>
+        <v>-0.2335</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.0451</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>1.192</v>
+        <v>-0.003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1971</v>
+        <v>0.0553</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9949</v>
+        <v>-0.0583</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1329</v>
+        <v>-1.2559</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6373</v>
+        <v>-0.0188</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5044</v>
+        <v>-1.2371</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.84</v>
+        <v>-1.8454</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6448</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1952</v>
+        <v>-0.8478</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6886</v>
+        <v>0.5374</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7268</v>
+        <v>-0.2492</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>0.7865</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1514</v>
+        <v>-2.3827</v>
       </c>
       <c r="N8" t="n">
-        <v>0.082</v>
+        <v>-0.7484</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2335</v>
+        <v>-1.6344</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0531</v>
+        <v>0.1751</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0565</v>
+        <v>-0.0336</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0034</v>
+        <v>0.2088</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>-0.0207</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8469</v>
+        <v>-1.7679</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3821</v>
+        <v>-3.488</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5351</v>
+        <v>1.7201</v>
       </c>
       <c r="G9" t="n">
         <v>-6.4482</v>
@@ -1156,13 +1156,13 @@
         <v>2.8276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7467</v>
+        <v>0.3323</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8099</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.2481</v>
       </c>
       <c r="V9" t="n">
         <v>1.5204</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6893</v>
+        <v>-4.1768</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1032</v>
+        <v>-2.9915</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.586</v>
+        <v>-1.1853</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4021</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4623</v>
+        <v>0.0502</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0156</v>
+        <v>0.1274</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4779</v>
+        <v>-0.0772</v>
       </c>
       <c r="V10" t="n">
         <v>-1.695</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1871</v>
+        <v>-4.7093</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8454</v>
+        <v>-2.3983</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3418</v>
+        <v>-2.311</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4937</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.781</v>
+        <v>-0.3031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.399</v>
+        <v>0.0481</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.382</v>
+        <v>-0.3512</v>
       </c>
       <c r="V11" t="n">
         <v>-1.695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8358999999999988</v>
+        <v>-0.8359999999999994</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5466</v>
+        <v>-4.546700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>3.710699999999998</v>
+        <v>3.7108</v>
       </c>
       <c r="G12" t="n">
         <v>-6.4781</v>
@@ -1369,7 +1369,7 @@
         <v>10.5559</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.6616</v>
+        <v>-5.661599999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-11.3723</v>
@@ -1390,13 +1390,13 @@
         <v>18.488</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6378</v>
+        <v>2.637799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7210000000000001</v>
+        <v>0.7211000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9166</v>
+        <v>1.916700000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.346</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4716</v>
+        <v>3.9582</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7543</v>
+        <v>2.7442</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7173</v>
+        <v>1.2139</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4933</v>
+        <v>4.4838</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5937</v>
+        <v>0.0302</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1004</v>
+        <v>4.4536</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4336</v>
+        <v>3.9309</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2806</v>
+        <v>0.1825</v>
       </c>
       <c r="L13" t="n">
-        <v>0.153</v>
+        <v>3.7484</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0597</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3131</v>
+        <v>-0.1523</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2534</v>
+        <v>0.7052</v>
       </c>
       <c r="P13" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R13" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5433</v>
+        <v>-0.1782</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7557</v>
+        <v>-0.0769</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7876</v>
+        <v>-0.1013</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.506</v>
+        <v>3.9353</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7442</v>
+        <v>2.4132</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7618</v>
+        <v>1.5221</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4838</v>
+        <v>1.4933</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0302</v>
+        <v>1.5937</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4536</v>
+        <v>-0.1004</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9309</v>
+        <v>1.4336</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1825</v>
+        <v>1.2806</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7484</v>
+        <v>0.153</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.0597</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1523</v>
+        <v>0.3131</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7052</v>
+        <v>-0.2534</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6303</v>
+        <v>1.007</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0769</v>
+        <v>0.4146</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5534</v>
+        <v>0.5924</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4464</v>
+        <v>3.6744</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5171</v>
+        <v>2.4112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9292</v>
+        <v>1.2632</v>
       </c>
       <c r="G15" t="n">
         <v>3.9382</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7093</v>
+        <v>-0.4813</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3699</v>
+        <v>-0.4759</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3394</v>
+        <v>-0.0054</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8653</v>
+        <v>1.6303</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9133</v>
+        <v>0.8015</v>
       </c>
       <c r="F16" t="n">
-        <v>0.952</v>
+        <v>0.8287</v>
       </c>
       <c r="G16" t="n">
         <v>1.456</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1918</v>
+        <v>-0.0433</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2002</v>
+        <v>0.0769</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4001</v>
+        <v>-0.0083</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3649</v>
+        <v>0.1414</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0352</v>
+        <v>-0.1498</v>
       </c>
       <c r="G17" t="n">
         <v>-2.2884</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4487</v>
+        <v>0.0403</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2319</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4571</v>
+        <v>0.2722</v>
       </c>
       <c r="V17" t="n">
         <v>0.9347</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7982</v>
+        <v>-0.9444</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.032</v>
+        <v>-1.2</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2338</v>
+        <v>0.2556</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2005</v>
+        <v>-0.1429</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8157</v>
+        <v>-0.0122</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6152</v>
+        <v>-0.1307</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8381</v>
+        <v>0.093</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6086</v>
+        <v>0.0547</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2295</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0386</v>
+        <v>-0.2359</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4243</v>
+        <v>-0.067</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3857</v>
+        <v>-0.1689</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4801</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.709</v>
+        <v>-0.149</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3942</v>
+        <v>-0.2055</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3148</v>
+        <v>0.0565</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2159</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2159</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2167</v>
+        <v>-1.5289</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2</v>
+        <v>-1.9875</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0167</v>
+        <v>0.4586</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1429</v>
+        <v>-0.8139</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0122</v>
+        <v>0.2188</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1307</v>
+        <v>-1.0327</v>
       </c>
       <c r="J19" t="n">
-        <v>0.093</v>
+        <v>-0.5756</v>
       </c>
       <c r="K19" t="n">
         <v>0.0547</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>-0.6303</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2359</v>
+        <v>-0.2383</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.067</v>
+        <v>0.1641</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1689</v>
+        <v>-0.4024</v>
       </c>
       <c r="P19" t="n">
         <v>-0.6525</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4213</v>
+        <v>-0.0625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2055</v>
+        <v>-0.3245</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2158</v>
+        <v>0.262</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.148</v>
+        <v>-1.6652</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2111</v>
+        <v>-2.5908</v>
       </c>
       <c r="F20" t="n">
-        <v>0.063</v>
+        <v>0.9256</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8139</v>
+        <v>-0.2005</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2188</v>
+        <v>-1.8157</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0327</v>
+        <v>1.6152</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5756</v>
+        <v>0.8381</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0547</v>
+        <v>0.6086</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6303</v>
+        <v>0.2295</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2383</v>
+        <v>-1.0386</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1641</v>
+        <v>-2.4243</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4024</v>
+        <v>1.3857</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6816</v>
+        <v>-0.158</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>-0.1646</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1336</v>
+        <v>0.0066</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2159</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2159</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4547</v>
+        <v>-2.4437</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2817</v>
+        <v>-2.7229</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1729</v>
+        <v>0.2792</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7417</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1458</v>
+        <v>-0.1349</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8904</v>
+        <v>-0.3317</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2554</v>
+        <v>0.1968</v>
       </c>
       <c r="V21" t="n">
         <v>0.3904</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2358</v>
+        <v>-4.2814</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2798</v>
+        <v>-3.721</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.956</v>
+        <v>-0.5604</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7058</v>
@@ -2170,13 +2170,13 @@
         <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9422</v>
+        <v>-0.9878</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9589</v>
+        <v>-0.4002</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9832</v>
+        <v>-0.5876</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8359999999999985</v>
+        <v>2.326300000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.710800000000002</v>
+        <v>-3.7107</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5467</v>
+        <v>6.0367</v>
       </c>
       <c r="G23" t="n">
         <v>6.4781</v>
@@ -2230,7 +2230,7 @@
         <v>4.968599999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.894400000000001</v>
+        <v>-4.894399999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-10.5559</v>
@@ -2248,13 +2248,13 @@
         <v>14.1378</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6377</v>
+        <v>-1.1477</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9165</v>
+        <v>-1.9168</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7210999999999999</v>
+        <v>0.7691</v>
       </c>
       <c r="V23" t="n">
         <v>1.3458</v>
